--- a/data/trans_dic/IP16A03-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,7</t>
+          <t>0,0; 13,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,82</t>
+          <t>0,0; 15,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 19,5</t>
+          <t>1,97; 21,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,67</t>
+          <t>0,0; 18,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,81</t>
+          <t>0,0; 19,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,52</t>
+          <t>1,19; 11,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 10,67</t>
+          <t>1,03; 12,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,32</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,19</t>
+          <t>0,0; 10,41</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 19,59</t>
+          <t>4,59; 20,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,02</t>
+          <t>0,0; 8,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,71</t>
+          <t>0,0; 12,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 12,74</t>
+          <t>1,49; 12,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,42</t>
+          <t>0,0; 8,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,08</t>
+          <t>0,0; 12,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 10,5</t>
+          <t>1,4; 10,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 13,2</t>
+          <t>3,68; 13,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,71</t>
+          <t>0,0; 6,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,78</t>
+          <t>0,0; 5,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,72</t>
+          <t>1,2; 8,1</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,39</t>
+          <t>0,0; 12,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 22,37</t>
+          <t>4,94; 23,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 16,55</t>
+          <t>1,64; 16,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,1</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 18,02</t>
+          <t>2,1; 19,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 14,57</t>
+          <t>1,7; 14,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,3</t>
+          <t>0,0; 18,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,93</t>
+          <t>0,0; 7,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 13,01</t>
+          <t>2,67; 13,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 14,15</t>
+          <t>3,85; 15,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 12,45</t>
+          <t>2,12; 12,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,9</t>
+          <t>0,23; 4,23</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,96</t>
+          <t>0,0; 13,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 13,64</t>
+          <t>1,67; 13,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,17</t>
+          <t>0,0; 10,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,15</t>
+          <t>0,0; 12,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 22,53</t>
+          <t>4,77; 20,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,34</t>
+          <t>0,0; 9,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 20,02</t>
+          <t>2,11; 20,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,8</t>
+          <t>0,0; 11,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 15,56</t>
+          <t>3,38; 14,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,81</t>
+          <t>0,99; 8,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,73</t>
+          <t>2,04; 11,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,58</t>
+          <t>0,96; 8,92</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 9,78</t>
+          <t>2,94; 9,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 8,02</t>
+          <t>2,24; 7,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,36</t>
+          <t>0,55; 4,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,48</t>
+          <t>0,44; 4,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 11,22</t>
+          <t>4,23; 11,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,26</t>
+          <t>1,7; 7,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,31</t>
+          <t>2,48; 9,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,31</t>
+          <t>1,62; 6,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,37</t>
+          <t>4,5; 9,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,28</t>
+          <t>2,53; 6,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,68</t>
+          <t>1,95; 5,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,52</t>
+          <t>1,35; 4,09</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1411</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4268</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4485</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>679; 7431</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4432</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5469</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>730; 6872</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>677; 8300</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3891</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5567</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4258</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2849</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6186</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1422</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3789</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1910; 8447</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3671</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5615</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>617; 5269</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3412</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5094</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>893; 6842</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3056; 11024</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4970</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4855</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1292; 8750</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3664</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1675</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1188</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2814</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1902</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3796</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5567</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3154</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3078</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1628; 7695</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>453; 4504</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>737; 6986</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>610; 5073</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5155</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4550</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1612; 7870</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2655; 10442</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1174; 7135</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>307; 5668</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2153</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4311</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4999</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3349</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3399</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699; 5767</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3585</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3738</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1850; 7997</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4660</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>637; 6278</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3822</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2179; 9498</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>884; 7664</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1281; 6920</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>615; 5745</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6564</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10465</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>6081</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>17740</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12634</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8590</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>8977</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3687; 12295</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3304; 11738</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>696; 5671</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>773; 7380</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6085; 16642</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2685; 12296</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3055; 11275</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2957; 11929</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>12127; 24861</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>7727; 19215</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4879; 14984</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4848; 14734</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A03-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Habitat-trans_dic.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,0</t>
+          <t>0,0; 15,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,64</t>
+          <t>0,0; 15,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 21,59</t>
+          <t>1,99; 22,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,33</t>
+          <t>0,0; 14,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 11,18</t>
+          <t>1,09; 10,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 12,6</t>
+          <t>1,02; 10,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 7,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,41</t>
+          <t>0,0; 10,02</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 20,28</t>
+          <t>4,29; 20,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,95</t>
+          <t>0,0; 7,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,69</t>
+          <t>0,0; 9,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 12,76</t>
+          <t>1,5; 12,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,46</t>
+          <t>0,0; 8,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,38</t>
+          <t>0,0; 11,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 10,72</t>
+          <t>1,33; 10,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 13,29</t>
+          <t>3,82; 13,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,11</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,79</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,1</t>
+          <t>1,29; 7,99</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,23</t>
+          <t>0,0; 13,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 23,34</t>
+          <t>4,89; 22,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 16,31</t>
+          <t>1,63; 17,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>0,0; 5,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 19,89</t>
+          <t>2,1; 20,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 14,09</t>
+          <t>1,69; 14,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,54</t>
+          <t>0,0; 16,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,99</t>
+          <t>0,0; 7,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 13,06</t>
+          <t>2,37; 12,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 15,14</t>
+          <t>3,79; 14,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 12,87</t>
+          <t>2,1; 14,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,23</t>
+          <t>0,27; 4,34</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,24</t>
+          <t>0,0; 13,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 13,8</t>
+          <t>1,67; 13,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,93</t>
+          <t>0,0; 8,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,23</t>
+          <t>0,0; 13,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 20,6</t>
+          <t>4,98; 23,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,87</t>
+          <t>0,0; 9,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 20,83</t>
+          <t>2,11; 21,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,3</t>
+          <t>0,0; 13,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 14,73</t>
+          <t>3,13; 14,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,61</t>
+          <t>0,83; 8,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 11,0</t>
+          <t>2,13; 10,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,92</t>
+          <t>0,92; 7,71</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,81</t>
+          <t>3,23; 9,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,97</t>
+          <t>2,36; 7,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,45</t>
+          <t>0,54; 4,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,15</t>
+          <t>0,46; 4,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 11,56</t>
+          <t>4,39; 11,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,78</t>
+          <t>1,85; 7,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,15</t>
+          <t>2,6; 9,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,55</t>
+          <t>1,64; 6,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 9,23</t>
+          <t>4,38; 9,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,3</t>
+          <t>2,38; 6,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,98</t>
+          <t>1,89; 5,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,09</t>
+          <t>1,32; 4,36</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4268</t>
+          <t>0; 5065</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1665,42 +1665,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4485</t>
+          <t>0; 4376</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>679; 7431</t>
+          <t>684; 7773</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4432</t>
+          <t>0; 3505</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5469</t>
+          <t>0; 5470</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>730; 6872</t>
+          <t>668; 6465</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>677; 8300</t>
+          <t>672; 7201</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3891</t>
+          <t>0; 3483</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5567</t>
+          <t>0; 5361</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1910; 8447</t>
+          <t>1787; 8405</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3671</t>
+          <t>0; 3028</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1868,47 +1868,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5615</t>
+          <t>0; 4383</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>617; 5269</t>
+          <t>621; 5245</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3412</t>
+          <t>0; 3449</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5094</t>
+          <t>0; 4539</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>893; 6842</t>
+          <t>850; 6932</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3056; 11024</t>
+          <t>3171; 10841</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4970</t>
+          <t>0; 4984</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4855</t>
+          <t>0; 4496</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1292; 8750</t>
+          <t>1397; 8638</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3078</t>
+          <t>0; 3364</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1628; 7695</t>
+          <t>1613; 7282</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>453; 4504</t>
+          <t>450; 4701</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4495</t>
+          <t>0; 4389</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>737; 6986</t>
+          <t>736; 7081</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>610; 5073</t>
+          <t>607; 5061</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5155</t>
+          <t>0; 4489</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4550</t>
+          <t>0; 4365</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1612; 7870</t>
+          <t>1432; 7523</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2655; 10442</t>
+          <t>2611; 10254</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1174; 7135</t>
+          <t>1162; 7802</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>307; 5668</t>
+          <t>361; 5814</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3399</t>
+          <t>0; 3528</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>699; 5767</t>
+          <t>697; 5674</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3585</t>
+          <t>0; 2925</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3738</t>
+          <t>0; 4244</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1850; 7997</t>
+          <t>1933; 8945</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4660</t>
+          <t>0; 4681</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>637; 6278</t>
+          <t>635; 6563</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3822</t>
+          <t>0; 4451</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2179; 9498</t>
+          <t>2018; 9301</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>884; 7664</t>
+          <t>736; 7612</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1281; 6920</t>
+          <t>1340; 6869</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>615; 5745</t>
+          <t>592; 4965</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3687; 12295</t>
+          <t>4042; 12371</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3304; 11738</t>
+          <t>3480; 11430</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>696; 5671</t>
+          <t>693; 5733</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>773; 7380</t>
+          <t>818; 7824</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6085; 16642</t>
+          <t>6322; 17167</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2685; 12296</t>
+          <t>2916; 11872</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3055; 11275</t>
+          <t>3205; 11629</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2957; 11929</t>
+          <t>2987; 11528</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12127; 24861</t>
+          <t>11788; 25026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7727; 19215</t>
+          <t>7275; 19237</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4879; 14984</t>
+          <t>4736; 14087</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4848; 14734</t>
+          <t>4735; 15681</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A03-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,11%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4,49%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,43</t>
+          <t>0,0; 14,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>1,97; 19,5</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 12,67</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,25</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 12,7</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 15,26</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,99; 22,58</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,5</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 19,77</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,51</t>
+          <t>1,18; 10,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 10,93</t>
+          <t>1,02; 10,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,18</t>
+          <t>0,0; 7,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,02</t>
+          <t>0,0; 4,31</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>10,22%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 20,18</t>
+          <t>1,49; 12,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,38</t>
+          <t>0,0; 9,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 13,08</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1,48; 11,78</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,39; 19,59</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 9,02</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,91</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,5; 12,7</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,55</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,03</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 10,86</t>
+          <t>0,0; 9,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 13,07</t>
+          <t>3,7; 13,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 5,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,0; 5,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,99</t>
+          <t>1,35; 8,26</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3,9%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11,12%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,06%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,37</t>
+          <t>2,06; 18,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 22,09</t>
+          <t>1,7; 14,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 17,02</t>
+          <t>0,0; 18,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,69</t>
+          <t>0,0; 8,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 20,16</t>
+          <t>0,0; 14,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 14,06</t>
+          <t>4,29; 22,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,14</t>
+          <t>1,63; 16,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,67</t>
+          <t>0,0; 9,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 12,48</t>
+          <t>2,42; 13,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 14,87</t>
+          <t>3,79; 14,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 14,08</t>
+          <t>1,7; 12,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,34</t>
+          <t>0,38; 6,02</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2,68%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,15%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,15%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -1137,37 +1137,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,74</t>
+          <t>4,05; 22,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 13,58</t>
+          <t>0,0; 10,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,92</t>
+          <t>2,26; 20,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,89</t>
+          <t>0,0; 12,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 23,04</t>
+          <t>0,0; 14,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,91</t>
+          <t>1,69; 13,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 21,77</t>
+          <t>0,0; 11,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 14,42</t>
+          <t>3,43; 15,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,55</t>
+          <t>0,84; 8,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 10,92</t>
+          <t>2,03; 11,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,71</t>
+          <t>0,94; 8,85</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,81%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,46%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,87</t>
+          <t>4,47; 11,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,76</t>
+          <t>1,67; 7,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,5</t>
+          <t>2,51; 9,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,4</t>
+          <t>1,48; 6,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 11,93</t>
+          <t>3,11; 9,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,52</t>
+          <t>2,27; 8,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,43</t>
+          <t>0,55; 4,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,33</t>
+          <t>0,53; 4,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 9,3</t>
+          <t>4,42; 9,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,3</t>
+          <t>2,62; 6,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,62</t>
+          <t>1,74; 5,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,36</t>
+          <t>1,4; 4,55</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1514,37 +1514,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,62 +1577,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1411</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1348</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1411</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>2605</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>677</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2760</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2605</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>392</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5065</t>
+          <t>0; 4249</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>677; 6712</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3063</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1784</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4169</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4376</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>684; 7773</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3505</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5470</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>668; 6465</t>
+          <t>727; 6472</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>672; 7201</t>
+          <t>674; 7026</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3483</t>
+          <t>0; 3553</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5361</t>
+          <t>0; 2193</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,62 +1785,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2692</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4258</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>747</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1928</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6186</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1422</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>1410</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2849</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6186</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1422</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3337</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1787; 8405</t>
+          <t>617; 5262</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3028</t>
+          <t>0; 3797</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0; 5384</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>837; 6652</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1828; 8159</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3700</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4383</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>621; 5245</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3449</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4539</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>850; 6932</t>
+          <t>0; 3451</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3171; 10841</t>
+          <t>3071; 10950</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4984</t>
+          <t>0; 4644</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4496</t>
+          <t>0; 4847</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1397; 8638</t>
+          <t>1252; 7649</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2814</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1902</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>981</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3664</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1675</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1188</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2814</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1902</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1479</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2087</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3364</t>
+          <t>724; 6329</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1613; 7282</t>
+          <t>611; 5245</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>450; 4701</t>
+          <t>0; 5090</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4389</t>
+          <t>0; 4656</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>736; 7081</t>
+          <t>0; 3621</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>607; 5061</t>
+          <t>1416; 7376</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4489</t>
+          <t>451; 4571</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4365</t>
+          <t>0; 4582</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1432; 7523</t>
+          <t>1457; 7841</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2611; 10254</t>
+          <t>2615; 9756</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1162; 7802</t>
+          <t>942; 6900</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>361; 5814</t>
+          <t>389; 6210</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4311</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1179</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>688</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2153</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4311</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2644</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>767</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1945</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3528</t>
+          <t>1573; 8746</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>697; 5674</t>
+          <t>0; 4883</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2925</t>
+          <t>680; 6036</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4244</t>
+          <t>0; 3817</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1933; 8945</t>
+          <t>0; 3842</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4681</t>
+          <t>706; 5699</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>635; 6563</t>
+          <t>0; 3663</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4451</t>
+          <t>0; 3914</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2018; 9301</t>
+          <t>2210; 10035</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>736; 7612</t>
+          <t>744; 7844</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1340; 6869</t>
+          <t>1275; 7382</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>592; 4965</t>
+          <t>576; 5420</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>10465</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>7275</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>6564</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2380</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6070</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>7761</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4042; 12371</t>
+          <t>6438; 16150</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3480; 11430</t>
+          <t>2640; 11462</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>693; 5733</t>
+          <t>3098; 11480</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>818; 7824</t>
+          <t>2440; 10178</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6322; 17167</t>
+          <t>3898; 12252</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2916; 11872</t>
+          <t>3342; 11801</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3205; 11629</t>
+          <t>706; 5554</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2987; 11528</t>
+          <t>763; 6885</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11788; 25026</t>
+          <t>11887; 25235</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7275; 19237</t>
+          <t>8004; 19176</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4736; 14087</t>
+          <t>4362; 14236</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4735; 15681</t>
+          <t>4306; 14012</t>
         </is>
       </c>
     </row>
